--- a/data/input/pureComponents_2026DecJANNAF_testing_actual.xlsx
+++ b/data/input/pureComponents_2026DecJANNAF_testing_actual.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099011B9-40D1-4886-A51F-7CC5CCDE8A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A1B47E-1746-4B0E-9BA5-988B7B07E565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
   </bookViews>
   <sheets>
     <sheet name="Unfinished CATALOG" sheetId="1" r:id="rId1"/>
     <sheet name="Pure Input" sheetId="2" r:id="rId2"/>
     <sheet name="Binary Input" sheetId="3" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unfinished CATALOG'!$A$1:$F$1</definedName>
   </definedNames>
@@ -884,8 +887,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="108">
   <si>
     <t>Full Name</t>
   </si>
@@ -1205,16 +1230,22 @@
     <t>[BH4-].C[N+](C)(C)C</t>
   </si>
   <si>
+    <t>[BH4-].CCCC[N+](CCCC)(CCCC)CCCC</t>
+  </si>
+  <si>
+    <t>B.N</t>
+  </si>
+  <si>
     <t>tetrabutylammonium borohydride</t>
-  </si>
-  <si>
-    <t>[BH4-].CCCC[N+](CCCC)(CCCC)CCCC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1251,9 +1282,18 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -1263,7 +1303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1276,6 +1316,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1291,6 +1334,2825 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="CATALOG"/>
+      <sheetName val="Chemical Names"/>
+      <sheetName val="Melting Temperature"/>
+      <sheetName val="Enthalpy of Fusion"/>
+      <sheetName val="Enthalpy of Formation"/>
+      <sheetName val="Binary SLE"/>
+      <sheetName val="Chemical Search"/>
+      <sheetName val="Chemical Generator"/>
+      <sheetName val="Input"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Chemical</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Standard Value</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E2">
+            <v>395</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>tetrabutylammonium chloride</v>
+          </cell>
+          <cell r="E3">
+            <v>314.14999999999998</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>tetrapentylammonium chloride</v>
+          </cell>
+          <cell r="E4">
+            <v>295.14999999999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>tetraheptylammonium chloride</v>
+          </cell>
+          <cell r="E5">
+            <v>264.14999999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E6">
+            <v>395.15</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>tetrapentylammonium bromide</v>
+          </cell>
+          <cell r="E7">
+            <v>376.15</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>tetrahexylammonium bromide</v>
+          </cell>
+          <cell r="E8">
+            <v>377.15</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>tetrabutylammonium iodide</v>
+          </cell>
+          <cell r="E9">
+            <v>419.15</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>tetrapentylammonium iodide</v>
+          </cell>
+          <cell r="E10">
+            <v>412.15</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>tetramethylammonium nitrate</v>
+          </cell>
+          <cell r="E11">
+            <v>683</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>tetrabutylammonium nitrate</v>
+          </cell>
+          <cell r="E12">
+            <v>388.4</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>tetrabutylammonium nitrate</v>
+          </cell>
+          <cell r="E13">
+            <v>389.3</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>tetrabutylammonium nitrate</v>
+          </cell>
+          <cell r="E14">
+            <v>392.2</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>tetrabutylammonium tetraphenylborate</v>
+          </cell>
+          <cell r="E15">
+            <v>502.2</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E16">
+            <v>447</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E17">
+            <v>612.87</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E18">
+            <v>693.15</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E19">
+            <v>526.78</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>tetrapropylammonium chloride</v>
+          </cell>
+          <cell r="E20">
+            <v>503.07</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>tetrapropylammonium chloride</v>
+          </cell>
+          <cell r="E21">
+            <v>416.15</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>ammonia</v>
+          </cell>
+          <cell r="E22">
+            <v>194.95</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>methyl bromide</v>
+          </cell>
+          <cell r="E23">
+            <v>179.5</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>methyl chloride</v>
+          </cell>
+          <cell r="E24">
+            <v>182</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>methyl chloride</v>
+          </cell>
+          <cell r="E25">
+            <v>175.55</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>methyl chloride</v>
+          </cell>
+          <cell r="E26">
+            <v>176.5</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>methyl iodide</v>
+          </cell>
+          <cell r="E27">
+            <v>206.7</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>methyl iodide</v>
+          </cell>
+          <cell r="E28">
+            <v>208.1</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>ethyl bromide</v>
+          </cell>
+          <cell r="E29">
+            <v>155</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>ethyl chloride</v>
+          </cell>
+          <cell r="E30">
+            <v>136.75</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>ethyl chloride</v>
+          </cell>
+          <cell r="E31">
+            <v>133</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>ethyl chloride</v>
+          </cell>
+          <cell r="E32">
+            <v>137</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>ethyl chloride</v>
+          </cell>
+          <cell r="E33">
+            <v>132.30000000000001</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>ethyl iodide</v>
+          </cell>
+          <cell r="E34">
+            <v>162.05000000000001</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>ethyl iodide</v>
+          </cell>
+          <cell r="E35">
+            <v>162.30000000000001</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E36">
+            <v>85.7</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E37">
+            <v>90.6</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E38">
+            <v>91.2</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E39">
+            <v>90.6</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E40">
+            <v>90.5</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E41">
+            <v>101</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E42">
+            <v>89.2</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>methylamine</v>
+          </cell>
+          <cell r="E43">
+            <v>180.05</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>methylamine</v>
+          </cell>
+          <cell r="E44">
+            <v>180.05</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>methylamine</v>
+          </cell>
+          <cell r="E45">
+            <v>179.7</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>propylamine</v>
+          </cell>
+          <cell r="E46">
+            <v>190.15</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E47">
+            <v>180.15</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E48">
+            <v>178.9</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E49">
+            <v>180.15</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E50">
+            <v>180.25</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E51">
+            <v>177.15</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E52">
+            <v>155.94999999999999</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E53">
+            <v>149.4</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E54">
+            <v>155.94999999999999</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E55">
+            <v>155.85</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E56">
+            <v>149.15</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>acetonitrile</v>
+          </cell>
+          <cell r="E57">
+            <v>228</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>propanenitrile</v>
+          </cell>
+          <cell r="E58">
+            <v>180</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>benzonitrile</v>
+          </cell>
+          <cell r="E59">
+            <v>263</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>butanenitrile</v>
+          </cell>
+          <cell r="E60">
+            <v>161.25</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>butanenitrile</v>
+          </cell>
+          <cell r="E61">
+            <v>161.15</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>butanenitrile</v>
+          </cell>
+          <cell r="E62">
+            <v>160</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>butanenitrile</v>
+          </cell>
+          <cell r="E63">
+            <v>161.25</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>butanenitrile</v>
+          </cell>
+          <cell r="E64">
+            <v>160.9</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E65">
+            <v>245.32</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E66">
+            <v>245.3</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67" t="str">
+            <v>hydrazine</v>
+          </cell>
+          <cell r="E67">
+            <v>275</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68" t="str">
+            <v>hydrazine</v>
+          </cell>
+          <cell r="E68">
+            <v>274.64999999999998</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69" t="str">
+            <v>hydrazine</v>
+          </cell>
+          <cell r="E69">
+            <v>275.14999999999998</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70" t="str">
+            <v>monomethylhydrazine</v>
+          </cell>
+          <cell r="E70">
+            <v>220.79</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71" t="str">
+            <v>monomethylhydrazine</v>
+          </cell>
+          <cell r="E71">
+            <v>220.8</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72" t="str">
+            <v>dimethylhydrazine</v>
+          </cell>
+          <cell r="E72">
+            <v>215.95</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73" t="str">
+            <v>dimethylhydrazine</v>
+          </cell>
+          <cell r="E73">
+            <v>216</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74" t="str">
+            <v>dinitrogen tetroxide</v>
+          </cell>
+          <cell r="E74">
+            <v>263.84999999999997</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75" t="str">
+            <v>dioxygen</v>
+          </cell>
+          <cell r="E75">
+            <v>327.95</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76" t="str">
+            <v>dinitrogen</v>
+          </cell>
+          <cell r="E76">
+            <v>63.049999999999983</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77" t="str">
+            <v>dinitrogen</v>
+          </cell>
+          <cell r="E77">
+            <v>63.149999999999977</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78" t="str">
+            <v>dinitrogen</v>
+          </cell>
+          <cell r="E78">
+            <v>63.139999999999986</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79" t="str">
+            <v>dihydrogen</v>
+          </cell>
+          <cell r="E79">
+            <v>14.009999999999991</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80" t="str">
+            <v>dihydrogen</v>
+          </cell>
+          <cell r="E80">
+            <v>13.989999999999952</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81" t="str">
+            <v>dihydrogen</v>
+          </cell>
+          <cell r="E81">
+            <v>13.799999999999955</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82" t="str">
+            <v>dichlorine</v>
+          </cell>
+          <cell r="E82">
+            <v>171.64999999999998</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83" t="str">
+            <v>dichlorine</v>
+          </cell>
+          <cell r="E83">
+            <v>171.64999999999998</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>dichlorine</v>
+          </cell>
+          <cell r="E84">
+            <v>171.64999999999998</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>lithium</v>
+          </cell>
+          <cell r="E85">
+            <v>453.68999999999994</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86" t="str">
+            <v>lithium</v>
+          </cell>
+          <cell r="E86">
+            <v>453.65</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87" t="str">
+            <v>lithium</v>
+          </cell>
+          <cell r="E87">
+            <v>453.68999999999994</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88" t="str">
+            <v>boron</v>
+          </cell>
+          <cell r="E88">
+            <v>2349.15</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89" t="str">
+            <v>boron</v>
+          </cell>
+          <cell r="E89">
+            <v>2348.15</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90" t="str">
+            <v>boron</v>
+          </cell>
+          <cell r="E90">
+            <v>2349.15</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91" t="str">
+            <v>sodium</v>
+          </cell>
+          <cell r="E91">
+            <v>370.87</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92" t="str">
+            <v>sodium</v>
+          </cell>
+          <cell r="E92">
+            <v>370.94399999999996</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93" t="str">
+            <v>sodium</v>
+          </cell>
+          <cell r="E93">
+            <v>370.96999999999997</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>sulfur</v>
+          </cell>
+          <cell r="E94">
+            <v>368.45</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95" t="str">
+            <v>sulfur</v>
+          </cell>
+          <cell r="E95">
+            <v>388.35999999999996</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96" t="str">
+            <v>sulfur</v>
+          </cell>
+          <cell r="E96">
+            <v>379.95</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97" t="str">
+            <v>potassium</v>
+          </cell>
+          <cell r="E97">
+            <v>336.53</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98" t="str">
+            <v>potassium</v>
+          </cell>
+          <cell r="E98">
+            <v>336.65</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99" t="str">
+            <v>potassium</v>
+          </cell>
+          <cell r="E99">
+            <v>336.53</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100" t="str">
+            <v>calcium</v>
+          </cell>
+          <cell r="E100">
+            <v>1115.1500000000001</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101" t="str">
+            <v>calcium</v>
+          </cell>
+          <cell r="E101">
+            <v>1115.1500000000001</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102" t="str">
+            <v>calcium</v>
+          </cell>
+          <cell r="E102">
+            <v>1115.1500000000001</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>sodium chloride</v>
+          </cell>
+          <cell r="E103">
+            <v>1074</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104" t="str">
+            <v>sodium chloride</v>
+          </cell>
+          <cell r="E104">
+            <v>1074</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105" t="str">
+            <v>sodium chloride</v>
+          </cell>
+          <cell r="E105">
+            <v>1074.1500000000001</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106" t="str">
+            <v>potassium chloride</v>
+          </cell>
+          <cell r="E106">
+            <v>1044.1500000000001</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107" t="str">
+            <v>lithium chloride</v>
+          </cell>
+          <cell r="E107">
+            <v>883.15</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108" t="str">
+            <v>lithium chloride</v>
+          </cell>
+          <cell r="E108">
+            <v>886.15</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109" t="str">
+            <v>lithium borohydride</v>
+          </cell>
+          <cell r="E109">
+            <v>559.15</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110" t="str">
+            <v>sodium borohydride</v>
+          </cell>
+          <cell r="E110">
+            <v>673.15</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111" t="str">
+            <v>potassium borohydride</v>
+          </cell>
+          <cell r="E111">
+            <v>878.15</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E112">
+            <v>612.87</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E113">
+            <v>535.4</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114" t="str">
+            <v>tetrapropylammonium chloride</v>
+          </cell>
+          <cell r="E114">
+            <v>502.4</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115" t="str">
+            <v>tetrabutylammonium chloride</v>
+          </cell>
+          <cell r="E115">
+            <v>342.82</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E116">
+            <v>633</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117" t="str">
+            <v>tetrapropylammonium bromide</v>
+          </cell>
+          <cell r="E117">
+            <v>583</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E118">
+            <v>390.8</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119" t="str">
+            <v>tetrapentylammonium bromide</v>
+          </cell>
+          <cell r="E119">
+            <v>375.9</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120" t="str">
+            <v>tetrahexylammonium bromide</v>
+          </cell>
+          <cell r="E120">
+            <v>370.6</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121" t="str">
+            <v>lithium chloride</v>
+          </cell>
+          <cell r="E121">
+            <v>874.15</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122" t="str">
+            <v>potassium chloride</v>
+          </cell>
+          <cell r="E122">
+            <v>1046.1500000000001</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123" t="str">
+            <v>rubidium chloride</v>
+          </cell>
+          <cell r="E123">
+            <v>982.15</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124" t="str">
+            <v>cesium chloride</v>
+          </cell>
+          <cell r="E124">
+            <v>918.15</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125" t="str">
+            <v>sodium nitrate</v>
+          </cell>
+          <cell r="E125">
+            <v>589.15</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126" t="str">
+            <v>potassium nitrate</v>
+          </cell>
+          <cell r="E126">
+            <v>612.15</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127" t="str">
+            <v>calcium nitrate</v>
+          </cell>
+          <cell r="E127">
+            <v>823.15</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128" t="str">
+            <v>sodium chloride</v>
+          </cell>
+          <cell r="E128">
+            <v>1074.1500000000001</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129" t="str">
+            <v>tetrabutylammonium borohydride</v>
+          </cell>
+          <cell r="E129">
+            <v>402.15</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130" t="str">
+            <v>ammonia borane</v>
+          </cell>
+          <cell r="E130">
+            <v>377.15</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131" t="str">
+            <v>ammonia borane</v>
+          </cell>
+          <cell r="E131">
+            <v>391.15</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132" t="str">
+            <v>methylamine borane</v>
+          </cell>
+          <cell r="E132">
+            <v>331.15</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133" t="str">
+            <v>dimethylamine borane</v>
+          </cell>
+          <cell r="E133">
+            <v>310.14999999999998</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134" t="str">
+            <v>trimethylamine borane</v>
+          </cell>
+          <cell r="E134">
+            <v>366.65</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135" t="str">
+            <v>tert-butylamine borane</v>
+          </cell>
+          <cell r="E135">
+            <v>369.15</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136" t="str">
+            <v>butylamine borane</v>
+          </cell>
+          <cell r="E136">
+            <v>243.24999999999997</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137" t="str">
+            <v>hexylamine borane</v>
+          </cell>
+          <cell r="E137">
+            <v>281.64999999999998</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138" t="str">
+            <v>octylamine borane</v>
+          </cell>
+          <cell r="E138">
+            <v>307.84999999999997</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139" t="str">
+            <v>decylamine borane</v>
+          </cell>
+          <cell r="E139">
+            <v>323.04999999999995</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140" t="str">
+            <v>dodecylamine borane</v>
+          </cell>
+          <cell r="E140">
+            <v>333.84999999999997</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141" t="str">
+            <v>tetradecylamine borane</v>
+          </cell>
+          <cell r="E141">
+            <v>342.45</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142" t="str">
+            <v>tetramethylammonium borohydride</v>
+          </cell>
+          <cell r="E142">
+            <v>503.15</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143" t="str">
+            <v>tetramethylammonium borohydride</v>
+          </cell>
+          <cell r="E143">
+            <v>508.15</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Chemical</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Standard Value</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E2">
+            <v>16.149999999999999</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>tetrabutylammonium chloride</v>
+          </cell>
+          <cell r="E3">
+            <v>20.501600000000003</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>tetrapentylammonium chloride</v>
+          </cell>
+          <cell r="E4">
+            <v>1.29704</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E5">
+            <v>15.480800000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>tetrapentylammonium bromide</v>
+          </cell>
+          <cell r="E6">
+            <v>41.421600000000005</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>tetrahexylammonium bromide</v>
+          </cell>
+          <cell r="E7">
+            <v>15.8992</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>tetrabutylammonium iodide</v>
+          </cell>
+          <cell r="E8">
+            <v>9.6231999999999989</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>tetrapentylammonium iodide</v>
+          </cell>
+          <cell r="E9">
+            <v>39.329600000000006</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>tetramethylammonium nitrate</v>
+          </cell>
+          <cell r="E10">
+            <v>37.200000000000003</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>tetrabutylammonium nitrate</v>
+          </cell>
+          <cell r="E11">
+            <v>14.3</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>tetrabutylammonium nitrate</v>
+          </cell>
+          <cell r="E12">
+            <v>15.6</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E13">
+            <v>20.3</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E14">
+            <v>20.49</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E15">
+            <v>51.24</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>tetrapropylammonium chloride</v>
+          </cell>
+          <cell r="E16">
+            <v>66.58</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>ammonia</v>
+          </cell>
+          <cell r="E17">
+            <v>5.6529999999999996</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>methyl bromide</v>
+          </cell>
+          <cell r="E18">
+            <v>5.98</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>methyl chloride</v>
+          </cell>
+          <cell r="E19">
+            <v>6.431</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>methyl chloride</v>
+          </cell>
+          <cell r="E20">
+            <v>6.42</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>methyl iodide</v>
+          </cell>
+          <cell r="E21">
+            <v>9.1199999999999992</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>ethyl chloride</v>
+          </cell>
+          <cell r="E22">
+            <v>4.452</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>ethyl chloride</v>
+          </cell>
+          <cell r="E23">
+            <v>4.45</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E24">
+            <v>0.93920000000000003</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E25">
+            <v>2.79</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E26">
+            <v>2.8570000000000002</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E27">
+            <v>2.7930000000000001</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>methylamine</v>
+          </cell>
+          <cell r="E28">
+            <v>6.1340000000000003</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>methylamine</v>
+          </cell>
+          <cell r="E29">
+            <v>6.13</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>propylamine</v>
+          </cell>
+          <cell r="E30">
+            <v>10.9742</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>propylamine</v>
+          </cell>
+          <cell r="E31">
+            <v>10.97</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>propylamine</v>
+          </cell>
+          <cell r="E32">
+            <v>10.625</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E33">
+            <v>5.9409999999999998</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E34">
+            <v>5.94</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E35">
+            <v>6.5439999999999996</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E36">
+            <v>6.54</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>acetonitrile</v>
+          </cell>
+          <cell r="E37">
+            <v>8.17</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>propanenitrile</v>
+          </cell>
+          <cell r="E38">
+            <v>5.03</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>benzonitrile</v>
+          </cell>
+          <cell r="E39">
+            <v>10.98</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>benzonitrile</v>
+          </cell>
+          <cell r="E40">
+            <v>10.98</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>benzonitrile</v>
+          </cell>
+          <cell r="E41">
+            <v>10.98</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>benzonitrile</v>
+          </cell>
+          <cell r="E42">
+            <v>10.98</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E43">
+            <v>8.109</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E44">
+            <v>8.11</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>monomethylhydrazine</v>
+          </cell>
+          <cell r="E45">
+            <v>10.417999999999999</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>monomethylhydrazine</v>
+          </cell>
+          <cell r="E46">
+            <v>10.42</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>dimethylhydrazine</v>
+          </cell>
+          <cell r="E47">
+            <v>10.0726</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>dimethylhydrazine</v>
+          </cell>
+          <cell r="E48">
+            <v>10.07</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>dinitrogen tetroxide</v>
+          </cell>
+          <cell r="E49">
+            <v>14.65</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>dioxygen</v>
+          </cell>
+          <cell r="E50">
+            <v>0.44400000000000001</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>dioxygen</v>
+          </cell>
+          <cell r="E51">
+            <v>0.44</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>dinitrogen</v>
+          </cell>
+          <cell r="E52">
+            <v>0.71</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>dinitrogen</v>
+          </cell>
+          <cell r="E53">
+            <v>0.72</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v>dihydrogen</v>
+          </cell>
+          <cell r="E54">
+            <v>0.12</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>dihydrogen</v>
+          </cell>
+          <cell r="E55">
+            <v>0.11700000000000001</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>dichlorine</v>
+          </cell>
+          <cell r="E56">
+            <v>6.4059999999999997</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>dichlorine</v>
+          </cell>
+          <cell r="E57">
+            <v>6.4</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>carbon</v>
+          </cell>
+          <cell r="E58">
+            <v>117</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>carbon</v>
+          </cell>
+          <cell r="E59">
+            <v>117</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>lithium</v>
+          </cell>
+          <cell r="E60">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>lithium</v>
+          </cell>
+          <cell r="E61">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>lithium</v>
+          </cell>
+          <cell r="E62">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>boron</v>
+          </cell>
+          <cell r="E63">
+            <v>50.2</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>boron</v>
+          </cell>
+          <cell r="E64">
+            <v>50.2</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65" t="str">
+            <v>boron</v>
+          </cell>
+          <cell r="E65">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66" t="str">
+            <v>sodium</v>
+          </cell>
+          <cell r="E66">
+            <v>2.6</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67" t="str">
+            <v>sodium</v>
+          </cell>
+          <cell r="E67">
+            <v>2.6</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68" t="str">
+            <v>sodium</v>
+          </cell>
+          <cell r="E68">
+            <v>2.6</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69" t="str">
+            <v>sulfur</v>
+          </cell>
+          <cell r="E69">
+            <v>1.72</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70" t="str">
+            <v>sulfur</v>
+          </cell>
+          <cell r="E70">
+            <v>1.7270000000000001</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71" t="str">
+            <v>sulfur</v>
+          </cell>
+          <cell r="E71">
+            <v>1.73</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72" t="str">
+            <v>potassium</v>
+          </cell>
+          <cell r="E72">
+            <v>2.33</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73" t="str">
+            <v>potassium</v>
+          </cell>
+          <cell r="E73">
+            <v>2.3210000000000002</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74" t="str">
+            <v>potassium</v>
+          </cell>
+          <cell r="E74">
+            <v>2.33</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75" t="str">
+            <v>calcium</v>
+          </cell>
+          <cell r="E75">
+            <v>8.5399999999999991</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76" t="str">
+            <v>calcium</v>
+          </cell>
+          <cell r="E76">
+            <v>8.5399999999999991</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77" t="str">
+            <v>calcium</v>
+          </cell>
+          <cell r="E77">
+            <v>8.5399999999999991</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78" t="str">
+            <v>sodium chloride</v>
+          </cell>
+          <cell r="E78">
+            <v>30.388680025600006</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79" t="str">
+            <v>lithium chloride</v>
+          </cell>
+          <cell r="E79">
+            <v>19.899999999999999</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80" t="str">
+            <v>lithium borohydride</v>
+          </cell>
+          <cell r="E80">
+            <v>7.14</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81" t="str">
+            <v>sodium borohydride</v>
+          </cell>
+          <cell r="E81">
+            <v>16</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82" t="str">
+            <v>potassium borohydride</v>
+          </cell>
+          <cell r="E82">
+            <v>19.2</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E83">
+            <v>20.49</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E84">
+            <v>51.24</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>tetrapropylammonium chloride</v>
+          </cell>
+          <cell r="E85">
+            <v>66.58</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86" t="str">
+            <v>tetrabutylammonium chloride</v>
+          </cell>
+          <cell r="E86">
+            <v>19.43</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E87">
+            <v>13.9</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88" t="str">
+            <v>tetrapropylammonium bromide</v>
+          </cell>
+          <cell r="E88">
+            <v>7.3</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E89">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90" t="str">
+            <v>tetrapentylammonium bromide</v>
+          </cell>
+          <cell r="E90">
+            <v>40.1</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91" t="str">
+            <v>tetrahexylammonium bromide</v>
+          </cell>
+          <cell r="E91">
+            <v>11.6</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92" t="str">
+            <v>potassium chloride</v>
+          </cell>
+          <cell r="E92">
+            <v>26.317360000000001</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93" t="str">
+            <v>tetrabutylammonium borohydride</v>
+          </cell>
+          <cell r="E93">
+            <v>17.8</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>tetrabutylammonium borohydride</v>
+          </cell>
+          <cell r="E94">
+            <v>15.8</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95" t="str">
+            <v>tetrabutylammonium tetrakis(borohydride)yttreate(III)</v>
+          </cell>
+          <cell r="E95">
+            <v>16.399999999999999</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96" t="str">
+            <v>ammonia borane</v>
+          </cell>
+          <cell r="E96">
+            <v>3.2</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97" t="str">
+            <v>ammonia borane</v>
+          </cell>
+          <cell r="E97">
+            <v>2.4</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98" t="str">
+            <v>methylamine borane</v>
+          </cell>
+          <cell r="E98">
+            <v>8.5</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99" t="str">
+            <v>methylamine borane</v>
+          </cell>
+          <cell r="E99">
+            <v>11.9</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100" t="str">
+            <v>butylamine borane</v>
+          </cell>
+          <cell r="E100">
+            <v>10.9</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101" t="str">
+            <v>hexylamine borane</v>
+          </cell>
+          <cell r="E101">
+            <v>15.4</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102" t="str">
+            <v>octylamine borane</v>
+          </cell>
+          <cell r="E102">
+            <v>23.6</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103" t="str">
+            <v>decylamine borane</v>
+          </cell>
+          <cell r="E103">
+            <v>30.7</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104" t="str">
+            <v>dodecylamine borane</v>
+          </cell>
+          <cell r="E104">
+            <v>39.6</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105" t="str">
+            <v>tetradecylamine borane</v>
+          </cell>
+          <cell r="E105">
+            <v>48.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Chemical</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Standard Value</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E2">
+            <v>-276</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E3">
+            <v>-272</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>tetramethylammonium chloride</v>
+          </cell>
+          <cell r="E4">
+            <v>-276.39999999999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>tetramethylammonium bromide</v>
+          </cell>
+          <cell r="E5">
+            <v>-251.5</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>tetramethylammonium bromide</v>
+          </cell>
+          <cell r="E6">
+            <v>-268</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>tetramethylammonium bromide</v>
+          </cell>
+          <cell r="E7">
+            <v>-251</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>tetramethylammonium iodide</v>
+          </cell>
+          <cell r="E8">
+            <v>-203.5</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>tetramethylammonium iodide</v>
+          </cell>
+          <cell r="E9">
+            <v>-190</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>tetramethylammonium iodide</v>
+          </cell>
+          <cell r="E10">
+            <v>-203.9</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E11">
+            <v>-400.8</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E12">
+            <v>-414</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E13">
+            <v>-401</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>tetraethylammonium chloride</v>
+          </cell>
+          <cell r="E14">
+            <v>-369.4</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E15">
+            <v>-374.1</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E16">
+            <v>-377</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E17">
+            <v>-360</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>tetraethylammonium bromide</v>
+          </cell>
+          <cell r="E18">
+            <v>-342.7</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>tetraethylammonium iodide</v>
+          </cell>
+          <cell r="E19">
+            <v>-331.5</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>tetraethylammonium iodide</v>
+          </cell>
+          <cell r="E20">
+            <v>-317</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>tetraethylammonium iodide</v>
+          </cell>
+          <cell r="E21">
+            <v>-316</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>tetraethylammonium iodide</v>
+          </cell>
+          <cell r="E22">
+            <v>-300.2</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>tetrapropylammonium chloride</v>
+          </cell>
+          <cell r="E23">
+            <v>-500</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24" t="str">
+            <v>tetrapropylammonium chloride</v>
+          </cell>
+          <cell r="E24">
+            <v>-475</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25" t="str">
+            <v>tetrapropylammonium bromide</v>
+          </cell>
+          <cell r="E25">
+            <v>-442</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26" t="str">
+            <v>tetrapropylammonium iodide</v>
+          </cell>
+          <cell r="E26">
+            <v>-395</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27" t="str">
+            <v>tetrabutylammonium chloride</v>
+          </cell>
+          <cell r="E27">
+            <v>-534</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>tetrabutylammonium chloride</v>
+          </cell>
+          <cell r="E28">
+            <v>-564.79999999999995</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E29">
+            <v>-415</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>tetrabutylammonium bromide</v>
+          </cell>
+          <cell r="E30">
+            <v>-540.29999999999995</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>tetrabutylammonium iodide</v>
+          </cell>
+          <cell r="E31">
+            <v>-460</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>tetrabutylammonium iodide</v>
+          </cell>
+          <cell r="E32">
+            <v>-498.6</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>tetramethylammonium nitrate</v>
+          </cell>
+          <cell r="E33">
+            <v>-331</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>tetramethylammonium nitrate</v>
+          </cell>
+          <cell r="E34">
+            <v>-331.8</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>tetramethylammonium nitrate</v>
+          </cell>
+          <cell r="E35">
+            <v>-328.5</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>tetramethylammonium nitrate</v>
+          </cell>
+          <cell r="E36">
+            <v>-330.3</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>tetraethylammonium nitrate</v>
+          </cell>
+          <cell r="E37">
+            <v>-428.5</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>tetraethylammonium nitrate</v>
+          </cell>
+          <cell r="E38">
+            <v>-433</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>tetraethylammonium nitrate</v>
+          </cell>
+          <cell r="E39">
+            <v>-431</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>tetrabutylammonium nitrate</v>
+          </cell>
+          <cell r="E40">
+            <v>-600.20000000000005</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>ammonia</v>
+          </cell>
+          <cell r="E41">
+            <v>-45.94</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>ammonia</v>
+          </cell>
+          <cell r="E42">
+            <v>-45.9</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>methyl bromide</v>
+          </cell>
+          <cell r="E43">
+            <v>-60.6</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>methyl chloride</v>
+          </cell>
+          <cell r="E44">
+            <v>-102.4</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>methyl iodide</v>
+          </cell>
+          <cell r="E45">
+            <v>-13.6</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>methyl iodide</v>
+          </cell>
+          <cell r="E46">
+            <v>-12</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>ethyl bromide</v>
+          </cell>
+          <cell r="E47">
+            <v>-95.5</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>ethyl chloride</v>
+          </cell>
+          <cell r="E48">
+            <v>-137</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>ethyl iodide</v>
+          </cell>
+          <cell r="E49">
+            <v>-39.1</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>ethyl iodide</v>
+          </cell>
+          <cell r="E50">
+            <v>-39.5</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>ethyl iodide</v>
+          </cell>
+          <cell r="E51">
+            <v>-35</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E52">
+            <v>-74.87</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E53">
+            <v>-74.599999999999994</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E54">
+            <v>-74.5</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E55">
+            <v>-74.849999999999994</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>methane</v>
+          </cell>
+          <cell r="E56">
+            <v>-73.400000000000006</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E57">
+            <v>-84</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E58">
+            <v>-83.8</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>ethane</v>
+          </cell>
+          <cell r="E59">
+            <v>-84.67</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>methylamine</v>
+          </cell>
+          <cell r="E60">
+            <v>-23.5</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>methylamine</v>
+          </cell>
+          <cell r="E61">
+            <v>-12.2</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>propylamine</v>
+          </cell>
+          <cell r="E62">
+            <v>-101.5</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>propylamine</v>
+          </cell>
+          <cell r="E63">
+            <v>-138</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E64">
+            <v>-19</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65" t="str">
+            <v>dimethylamine</v>
+          </cell>
+          <cell r="E65">
+            <v>-23.8</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E66">
+            <v>-23.7</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67" t="str">
+            <v>trimethylamine</v>
+          </cell>
+          <cell r="E67">
+            <v>-30.7</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68" t="str">
+            <v>acetonitrile</v>
+          </cell>
+          <cell r="E68">
+            <v>40.56</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69" t="str">
+            <v>acetonitrile</v>
+          </cell>
+          <cell r="E69">
+            <v>31.4</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70" t="str">
+            <v>propanenitrile</v>
+          </cell>
+          <cell r="E70">
+            <v>15.5</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71" t="str">
+            <v>benzonitrile</v>
+          </cell>
+          <cell r="E71">
+            <v>163.19999999999999</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72" t="str">
+            <v>benzonitrile</v>
+          </cell>
+          <cell r="E72">
+            <v>163.19999999999999</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73" t="str">
+            <v>butanenitrile</v>
+          </cell>
+          <cell r="E73">
+            <v>-5.8</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E74">
+            <v>309.07</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E75">
+            <v>308.89999999999998</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E76">
+            <v>263</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77" t="str">
+            <v>cyanogen</v>
+          </cell>
+          <cell r="E77">
+            <v>306.7</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78" t="str">
+            <v>hydrazine</v>
+          </cell>
+          <cell r="E78">
+            <v>50.63</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79" t="str">
+            <v>monomethylhydrazine</v>
+          </cell>
+          <cell r="E79">
+            <v>54.14</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80" t="str">
+            <v>dimethylhydrazine</v>
+          </cell>
+          <cell r="E80">
+            <v>48.3</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81" t="str">
+            <v>dinitrogen tetroxide</v>
+          </cell>
+          <cell r="E81">
+            <v>9.08</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82" t="str">
+            <v>dioxygen</v>
+          </cell>
+          <cell r="E82">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83" t="str">
+            <v>dinitrogen</v>
+          </cell>
+          <cell r="E83">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>dihydrogen</v>
+          </cell>
+          <cell r="E84">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>dichlorine</v>
+          </cell>
+          <cell r="E85">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86" t="str">
+            <v>carbon</v>
+          </cell>
+          <cell r="E86">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87" t="str">
+            <v>lithium</v>
+          </cell>
+          <cell r="E87">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88" t="str">
+            <v>boron</v>
+          </cell>
+          <cell r="E88">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89" t="str">
+            <v>sodium</v>
+          </cell>
+          <cell r="E89">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90" t="str">
+            <v>sulfur</v>
+          </cell>
+          <cell r="E90">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91" t="str">
+            <v>potassium</v>
+          </cell>
+          <cell r="E91">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92" t="str">
+            <v>calcium</v>
+          </cell>
+          <cell r="E92">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93" t="str">
+            <v>sodium chloride</v>
+          </cell>
+          <cell r="E93">
+            <v>-410.9</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94" t="str">
+            <v>sodium chloride</v>
+          </cell>
+          <cell r="E94">
+            <v>-411.12</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95" t="str">
+            <v>potassium chloride</v>
+          </cell>
+          <cell r="E95">
+            <v>-436.68</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96" t="str">
+            <v>lithium chloride</v>
+          </cell>
+          <cell r="E96">
+            <v>-408.6</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97" t="str">
+            <v>lithium borohydride</v>
+          </cell>
+          <cell r="E97">
+            <v>-190.46</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98" t="str">
+            <v>sodium borohydride</v>
+          </cell>
+          <cell r="E98">
+            <v>-191.84</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99" t="str">
+            <v>potassium borohydride</v>
+          </cell>
+          <cell r="E99">
+            <v>-226.9</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100" t="str">
+            <v>ammonia borane</v>
+          </cell>
+          <cell r="E100">
+            <v>-133.4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2229,41 +5091,50 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
-        <f>1.96*9.89949493661167/SQRT(F2)</f>
-        <v>13.720000000000006</v>
+        <v>106</v>
+      </c>
+      <c r="D2" s="6">
+        <f>IFERROR(AVERAGEIF('[1]Melting Temperature'!$A:$A, $A2, '[1]Melting Temperature'!$E:$E), "—")</f>
+        <v>384.15</v>
+      </c>
+      <c r="E2" cm="1">
+        <f t="array" ref="E2">IFERROR(IF(COUNTIF('[1]Melting Temperature'!$A:$A, $A2)&gt;1, _xlfn.STDEV.S(_xlfn._xlws.FILTER('[1]Melting Temperature'!$E:$E, '[1]Melting Temperature'!$A:$A=$A2)), "—"), "—")</f>
+        <v>9.8994949366116654</v>
       </c>
       <c r="F2">
+        <f>COUNTIF('[1]Melting Temperature'!$A:$A, $A2)</f>
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="6">
+        <f>IFERROR(AVERAGEIF('[1]Enthalpy of Fusion'!$A:$A, $A2, '[1]Enthalpy of Fusion'!$E:$E), "—")</f>
         <v>2.8</v>
       </c>
-      <c r="H2">
-        <f>1.96*0.56568542494924/SQRT(I2)</f>
-        <v>0.78400000000000269</v>
+      <c r="H2" cm="1">
+        <f t="array" ref="H2">IFERROR(IF(COUNTIF('[1]Enthalpy of Fusion'!$A:$A, $A2)&gt;1, _xlfn.STDEV.S(_xlfn._xlws.FILTER('[1]Enthalpy of Fusion'!$E:$E, '[1]Enthalpy of Fusion'!$A:$A=$A2)), "—"), "—")</f>
+        <v>0.56568542494923979</v>
       </c>
       <c r="I2">
+        <f>COUNTIF('[1]Enthalpy of Fusion'!$A:$A, $A2)</f>
         <v>2</v>
       </c>
-      <c r="J2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" t="s">
-        <v>101</v>
+      <c r="J2" s="7">
+        <f>IFERROR(AVERAGEIF('[1]Enthalpy of Formation'!$A:$A, $A2, '[1]Enthalpy of Formation'!$E:$E), "—")</f>
+        <v>-133.4</v>
+      </c>
+      <c r="K2" s="8">
+        <v>5.2</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <f>COUNTIF('[1]Enthalpy of Formation'!$A:$A, $A2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>103</v>
       </c>
       <c r="C3" t="s">
@@ -2299,11 +5170,11 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" t="s">
         <v>105</v>
-      </c>
-      <c r="C4" t="s">
-        <v>106</v>
       </c>
       <c r="D4">
         <v>402.15</v>
